--- a/artfynd/A 52630-2025 artfynd.xlsx
+++ b/artfynd/A 52630-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700017</v>
       </c>
       <c r="B2" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>127700030</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52630-2025 artfynd.xlsx
+++ b/artfynd/A 52630-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127700030</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52630-2025 artfynd.xlsx
+++ b/artfynd/A 52630-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127700030</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52630-2025 artfynd.xlsx
+++ b/artfynd/A 52630-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127700030</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52630-2025 artfynd.xlsx
+++ b/artfynd/A 52630-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127700030</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52630-2025 artfynd.xlsx
+++ b/artfynd/A 52630-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127700030</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52630-2025 artfynd.xlsx
+++ b/artfynd/A 52630-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127700030</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52630-2025 artfynd.xlsx
+++ b/artfynd/A 52630-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127700017</v>
+        <v>127700016</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>784699</v>
+        <v>784815</v>
       </c>
       <c r="R2" t="n">
-        <v>7184415</v>
+        <v>7184343</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,45 +784,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700030</v>
+        <v>127700017</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784693</v>
+        <v>784699</v>
       </c>
       <c r="R3" t="n">
-        <v>7184420</v>
+        <v>7184415</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +865,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,6 +891,309 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127700021</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stöverberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>784804</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7184227</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127700030</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stöverberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>784693</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7184420</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127700032</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stöverberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>784810</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7184264</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>

--- a/artfynd/A 52630-2025 artfynd.xlsx
+++ b/artfynd/A 52630-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700016</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700021</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700030</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,8 +1223,20 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700032</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>